--- a/data/trans_dic/P3A_R1-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R1-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,72; 25,52</t>
+          <t>15,36; 25,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,35; 36,17</t>
+          <t>23,38; 34,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,53; 37,2</t>
+          <t>25,62; 37,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,32; 30,31</t>
+          <t>20,13; 30,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,7; 19,52</t>
+          <t>11,29; 20,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,68; 12,81</t>
+          <t>5,85; 12,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,74; 18,27</t>
+          <t>10,01; 18,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,66; 31,57</t>
+          <t>22,44; 31,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,38; 20,74</t>
+          <t>14,34; 20,98</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,98; 23,01</t>
+          <t>16,15; 22,93</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19,11; 26,36</t>
+          <t>18,72; 25,9</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,26; 29,12</t>
+          <t>22,49; 29,14</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,55; 29,57</t>
+          <t>21,29; 29,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,52; 28,79</t>
+          <t>20,57; 28,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,37; 33,67</t>
+          <t>24,9; 33,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34,71; 45,84</t>
+          <t>34,8; 45,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,2; 17,48</t>
+          <t>11,23; 17,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,15; 16,25</t>
+          <t>9,7; 16,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,82; 19,63</t>
+          <t>12,67; 18,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>27,27; 34,16</t>
+          <t>27,19; 34,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,22; 22,45</t>
+          <t>16,99; 22,16</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,07; 21,22</t>
+          <t>16,02; 21,15</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20,02; 25,29</t>
+          <t>19,78; 24,94</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>32,06; 38,65</t>
+          <t>32,24; 38,68</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,79; 23,67</t>
+          <t>14,86; 23,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20,67; 30,62</t>
+          <t>20,73; 30,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35,36; 45,81</t>
+          <t>35,16; 45,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28,5; 38,08</t>
+          <t>28,08; 38,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,32; 11,23</t>
+          <t>5,39; 11,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,4; 14,3</t>
+          <t>7,09; 14,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,67; 27,14</t>
+          <t>18,06; 27,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24,38; 32,62</t>
+          <t>24,42; 32,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,54; 16,04</t>
+          <t>10,54; 16,2</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15,17; 20,77</t>
+          <t>15,04; 20,95</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27,13; 34,75</t>
+          <t>27,67; 35,01</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>27,25; 33,93</t>
+          <t>27,72; 33,88</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,55; 25,12</t>
+          <t>16,45; 25,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,93; 35,18</t>
+          <t>24,98; 34,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,84; 36,73</t>
+          <t>26,97; 37,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,2; 39,17</t>
+          <t>25,99; 38,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,63; 22,63</t>
+          <t>15,05; 22,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,27; 16,05</t>
+          <t>9,39; 16,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,88; 16,83</t>
+          <t>9,92; 17,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,6; 18,99</t>
+          <t>9,07; 19,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,75; 22,47</t>
+          <t>16,75; 22,52</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,11; 24,03</t>
+          <t>18,04; 24,1</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19,24; 25,58</t>
+          <t>19,39; 25,58</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,55; 26,13</t>
+          <t>15,4; 25,75</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,91; 27,11</t>
+          <t>15,62; 27,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,53; 25,05</t>
+          <t>13,93; 24,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,35; 42,71</t>
+          <t>29,86; 42,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,35; 28,99</t>
+          <t>18,67; 28,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,08; 16,09</t>
+          <t>6,86; 15,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,36; 19,97</t>
+          <t>10,89; 20,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,68; 23,89</t>
+          <t>13,63; 24,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,23; 23,52</t>
+          <t>9,92; 24,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,42; 19,2</t>
+          <t>12,44; 19,81</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13,59; 20,91</t>
+          <t>13,53; 20,75</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22,82; 31,97</t>
+          <t>23,23; 31,63</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,94; 24,02</t>
+          <t>13,67; 24,47</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,31; 22,65</t>
+          <t>13,42; 22,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24,81; 36,09</t>
+          <t>23,92; 36,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,04; 31,03</t>
+          <t>20,11; 31,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>34,39; 45,78</t>
+          <t>34,22; 45,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,25; 17,37</t>
+          <t>9,26; 17,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,98; 23,31</t>
+          <t>14,08; 24,12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,11; 15,78</t>
+          <t>8,1; 16,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>32,38; 42,16</t>
+          <t>32,97; 42,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12,34; 18,52</t>
+          <t>12,25; 18,63</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20,53; 28,28</t>
+          <t>20,31; 28,03</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14,95; 21,74</t>
+          <t>14,97; 21,94</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>34,99; 42,21</t>
+          <t>35,36; 42,33</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>19,98; 27,18</t>
+          <t>20,0; 27,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>23,83; 31,12</t>
+          <t>23,87; 31,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25,51; 32,85</t>
+          <t>24,64; 32,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24,39; 31,88</t>
+          <t>23,94; 31,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,41; 13,21</t>
+          <t>8,41; 13,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,84; 20,87</t>
+          <t>14,82; 20,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,1; 26,53</t>
+          <t>20,02; 26,21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,63; 24,84</t>
+          <t>9,21; 24,74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,96; 19,23</t>
+          <t>14,8; 19,07</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20,38; 25,06</t>
+          <t>20,25; 24,72</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23,49; 28,36</t>
+          <t>23,6; 28,5</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,77; 26,68</t>
+          <t>14,41; 26,58</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>15,99; 21,85</t>
+          <t>15,65; 21,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>26,69; 33,61</t>
+          <t>26,54; 33,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32,27; 39,44</t>
+          <t>32,58; 39,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,35; 18,08</t>
+          <t>5,49; 17,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,72; 11,84</t>
+          <t>7,64; 11,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,53; 20,12</t>
+          <t>14,63; 20,16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,94; 24,66</t>
+          <t>19,08; 24,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,86; 6,37</t>
+          <t>3,85; 6,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12,3; 15,67</t>
+          <t>11,98; 15,74</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21,16; 25,63</t>
+          <t>21,42; 25,97</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26,47; 30,99</t>
+          <t>26,52; 30,89</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,86; 11,5</t>
+          <t>5,9; 11,61</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>19,39; 22,27</t>
+          <t>19,56; 22,49</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>25,89; 29,0</t>
+          <t>25,84; 29,09</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30,85; 34,21</t>
+          <t>30,71; 34,14</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21,19; 29,56</t>
+          <t>21,24; 29,71</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10,9; 13,14</t>
+          <t>11,0; 13,21</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,57; 16,09</t>
+          <t>13,71; 16,05</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,28; 19,96</t>
+          <t>17,24; 19,87</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16,28; 21,65</t>
+          <t>15,97; 21,81</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>15,51; 17,22</t>
+          <t>15,48; 17,36</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>20,02; 22,05</t>
+          <t>20,05; 22,17</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>24,19; 26,37</t>
+          <t>24,2; 26,41</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>20,2; 25,03</t>
+          <t>20,28; 25,16</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>42926; 69675</t>
+          <t>41940; 69426</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>71763; 106593</t>
+          <t>68895; 102970</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>74992; 109285</t>
+          <t>75255; 109637</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>60182; 94411</t>
+          <t>62694; 94244</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>27802; 50708</t>
+          <t>29334; 52839</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16311; 36794</t>
+          <t>16806; 36732</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28127; 52755</t>
+          <t>28888; 52408</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>65639; 91440</t>
+          <t>64989; 90416</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>76625; 110524</t>
+          <t>76402; 111791</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>92979; 133905</t>
+          <t>93967; 133437</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>111321; 153522</t>
+          <t>109042; 150883</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>133821; 175045</t>
+          <t>135184; 175178</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>106249; 145826</t>
+          <t>104999; 144529</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>103533; 145213</t>
+          <t>103762; 143181</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>126580; 167967</t>
+          <t>124199; 168103</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>179957; 237616</t>
+          <t>180391; 237390</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>56459; 88082</t>
+          <t>56593; 87616</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53187; 85117</t>
+          <t>50814; 86872</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>66921; 102493</t>
+          <t>66147; 98814</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>140429; 175907</t>
+          <t>140027; 177113</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>171681; 223862</t>
+          <t>169398; 220959</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>165221; 218192</t>
+          <t>164720; 217491</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>204408; 258237</t>
+          <t>201964; 254614</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>331284; 399349</t>
+          <t>333121; 399678</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>47169; 75465</t>
+          <t>47375; 75477</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>66993; 99228</t>
+          <t>67165; 98040</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>112382; 145605</t>
+          <t>111742; 146178</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>89898; 120116</t>
+          <t>88559; 120478</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>17833; 37652</t>
+          <t>18087; 37788</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25221; 48768</t>
+          <t>24189; 49818</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>59422; 91271</t>
+          <t>60725; 91434</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>84802; 113464</t>
+          <t>84964; 113820</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>68962; 104974</t>
+          <t>68946; 106019</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>100915; 138165</t>
+          <t>99994; 139324</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>177441; 227313</t>
+          <t>181023; 228990</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>180734; 225080</t>
+          <t>183896; 224717</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>59357; 90100</t>
+          <t>59011; 91202</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>93232; 131581</t>
+          <t>93403; 130589</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>98798; 135179</t>
+          <t>99270; 136456</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>81889; 122425</t>
+          <t>81245; 121159</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>54181; 83811</t>
+          <t>55734; 84101</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36055; 62435</t>
+          <t>36533; 63359</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38249; 65184</t>
+          <t>38400; 66325</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>40896; 90340</t>
+          <t>43141; 90449</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>122108; 163831</t>
+          <t>122086; 164157</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>138183; 183344</t>
+          <t>137609; 183836</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>145315; 193193</t>
+          <t>146457; 193190</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>122586; 205941</t>
+          <t>121410; 203012</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>32345; 55114</t>
+          <t>31753; 55612</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>28776; 53268</t>
+          <t>29623; 52754</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>61993; 90219</t>
+          <t>63065; 90728</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32710; 51688</t>
+          <t>33277; 51357</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>14700; 33423</t>
+          <t>14250; 32905</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22743; 43856</t>
+          <t>23915; 44286</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29780; 51982</t>
+          <t>29658; 52438</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>23886; 60860</t>
+          <t>25661; 62827</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>51033; 78892</t>
+          <t>51105; 81412</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>58742; 90369</t>
+          <t>58473; 89687</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>97874; 137094</t>
+          <t>99627; 135657</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>56569; 104969</t>
+          <t>59748; 106948</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>36057; 61333</t>
+          <t>36349; 61183</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>67975; 98878</t>
+          <t>65543; 99318</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>52395; 81134</t>
+          <t>52581; 81784</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>92723; 123438</t>
+          <t>92266; 122737</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>25719; 48307</t>
+          <t>25747; 48892</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>39150; 65289</t>
+          <t>39431; 67552</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22056; 42937</t>
+          <t>22048; 43582</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>83232; 108378</t>
+          <t>84746; 109064</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>67767; 101665</t>
+          <t>67263; 102249</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>113735; 156655</t>
+          <t>112501; 155293</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>79765; 115986</t>
+          <t>79895; 117065</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>184306; 222315</t>
+          <t>186214; 222961</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>122867; 167145</t>
+          <t>122988; 166645</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>157939; 206257</t>
+          <t>158231; 208246</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>167229; 215340</t>
+          <t>161502; 212311</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>152281; 199028</t>
+          <t>149464; 197972</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>53490; 84002</t>
+          <t>53500; 85452</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>102960; 144796</t>
+          <t>102849; 145062</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>138519; 182829</t>
+          <t>138010; 180688</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>81756; 210953</t>
+          <t>78233; 210099</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>187144; 240543</t>
+          <t>185182; 238563</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>276536; 340038</t>
+          <t>274663; 335323</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>315867; 381431</t>
+          <t>317327; 383273</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>202956; 393207</t>
+          <t>212344; 391704</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>118807; 162336</t>
+          <t>116251; 162547</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>207953; 261822</t>
+          <t>206787; 261125</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>251284; 307049</t>
+          <t>253644; 307319</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>49714; 167959</t>
+          <t>50961; 165997</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>60485; 92784</t>
+          <t>59892; 93498</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>119456; 165367</t>
+          <t>120199; 165644</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>156438; 203761</t>
+          <t>157594; 204161</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>27725; 45701</t>
+          <t>27615; 46736</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>187793; 239243</t>
+          <t>182938; 240295</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>338694; 410267</t>
+          <t>342880; 415827</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>424774; 497314</t>
+          <t>425627; 495660</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>96421; 189338</t>
+          <t>97086; 191103</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>635310; 729493</t>
+          <t>640571; 736856</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>886882; 993468</t>
+          <t>885148; 996643</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1044449; 1158096</t>
+          <t>1039782; 1155736</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>732759; 1022406</t>
+          <t>734467; 1027734</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>367940; 443267</t>
+          <t>371045; 445792</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>482746; 572044</t>
+          <t>487569; 570891</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>611538; 706442</t>
+          <t>610279; 703337</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>604305; 803283</t>
+          <t>592589; 809525</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1031181; 1145058</t>
+          <t>1029471; 1154499</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1397854; 1539790</t>
+          <t>1400238; 1548024</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1674992; 1826342</t>
+          <t>1676119; 1828966</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1448600; 1794625</t>
+          <t>1453819; 1803776</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A_R1-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R1-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>24,6%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,36; 25,43</t>
+          <t>15,09; 25,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,38; 34,94</t>
+          <t>23,64; 35,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,62; 37,32</t>
+          <t>25,32; 36,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20,13; 30,26</t>
+          <t>19,92; 29,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,29; 20,34</t>
+          <t>10,88; 19,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,85; 12,79</t>
+          <t>5,9; 13,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,01; 18,15</t>
+          <t>9,6; 18,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,44; 31,22</t>
+          <t>20,88; 28,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,34; 20,98</t>
+          <t>14,29; 20,96</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,15; 22,93</t>
+          <t>16,02; 23,05</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,72; 25,9</t>
+          <t>18,86; 26,11</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,49; 29,14</t>
+          <t>21,72; 27,95</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>36,37%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,29; 29,31</t>
+          <t>21,62; 30,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,57; 28,38</t>
+          <t>20,5; 28,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,9; 33,7</t>
+          <t>25,58; 33,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34,8; 45,79</t>
+          <t>36,53; 46,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,23; 17,39</t>
+          <t>11,11; 17,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,7; 16,59</t>
+          <t>10,01; 16,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,67; 18,92</t>
+          <t>12,49; 19,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>27,19; 34,39</t>
+          <t>27,41; 34,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,99; 22,16</t>
+          <t>17,29; 22,11</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,02; 21,15</t>
+          <t>16,31; 21,24</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19,78; 24,94</t>
+          <t>20,02; 25,0</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>32,24; 38,68</t>
+          <t>33,08; 39,69</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,69%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,86; 23,67</t>
+          <t>14,25; 23,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20,73; 30,26</t>
+          <t>21,13; 30,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35,16; 45,99</t>
+          <t>35,05; 45,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28,08; 38,2</t>
+          <t>27,29; 37,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,39; 11,27</t>
+          <t>4,96; 10,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,09; 14,61</t>
+          <t>7,24; 14,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,06; 27,19</t>
+          <t>17,81; 26,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24,42; 32,72</t>
+          <t>24,95; 32,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,54; 16,2</t>
+          <t>10,61; 16,16</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15,04; 20,95</t>
+          <t>15,01; 21,06</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27,67; 35,01</t>
+          <t>27,3; 34,54</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>27,72; 33,88</t>
+          <t>27,63; 33,9</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>24,63%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,45; 25,43</t>
+          <t>16,61; 25,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,98; 34,92</t>
+          <t>24,59; 34,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,97; 37,07</t>
+          <t>26,83; 37,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,99; 38,76</t>
+          <t>25,35; 38,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,05; 22,71</t>
+          <t>15,01; 22,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,39; 16,29</t>
+          <t>9,44; 16,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,92; 17,13</t>
+          <t>9,98; 17,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,07; 19,01</t>
+          <t>14,97; 21,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,75; 22,52</t>
+          <t>16,58; 22,5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,04; 24,1</t>
+          <t>18,09; 24,23</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19,39; 25,58</t>
+          <t>19,25; 25,39</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,4; 25,75</t>
+          <t>21,16; 28,44</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>22,9%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,62; 27,35</t>
+          <t>14,66; 26,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,93; 24,81</t>
+          <t>14,22; 24,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,86; 42,95</t>
+          <t>29,46; 42,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,67; 28,81</t>
+          <t>18,55; 28,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,86; 15,85</t>
+          <t>6,86; 15,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,89; 20,17</t>
+          <t>10,63; 20,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,63; 24,09</t>
+          <t>13,98; 24,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,92; 24,28</t>
+          <t>18,81; 26,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,44; 19,81</t>
+          <t>12,51; 19,34</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13,53; 20,75</t>
+          <t>13,7; 20,89</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23,23; 31,63</t>
+          <t>23,24; 31,68</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,67; 24,47</t>
+          <t>19,85; 26,02</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,73%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,42; 22,59</t>
+          <t>13,1; 22,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23,92; 36,25</t>
+          <t>25,29; 36,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,11; 31,28</t>
+          <t>20,28; 31,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>34,22; 45,52</t>
+          <t>35,13; 45,81</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,26; 17,58</t>
+          <t>9,36; 17,1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,08; 24,12</t>
+          <t>14,07; 23,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,1; 16,02</t>
+          <t>8,27; 16,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>32,97; 42,43</t>
+          <t>32,09; 41,52</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12,25; 18,63</t>
+          <t>12,46; 18,27</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20,31; 28,03</t>
+          <t>20,59; 28,46</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14,97; 21,94</t>
+          <t>15,18; 21,85</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>35,36; 42,33</t>
+          <t>35,43; 42,27</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>26,05%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>20,0; 27,1</t>
+          <t>20,12; 26,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>23,87; 31,42</t>
+          <t>24,04; 31,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24,64; 32,39</t>
+          <t>25,57; 32,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23,94; 31,71</t>
+          <t>25,64; 33,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,41; 13,44</t>
+          <t>8,42; 13,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,82; 20,91</t>
+          <t>14,65; 21,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,02; 26,21</t>
+          <t>19,81; 26,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,21; 24,74</t>
+          <t>20,65; 26,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,8; 19,07</t>
+          <t>14,92; 19,09</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20,25; 24,72</t>
+          <t>20,16; 24,73</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23,6; 28,5</t>
+          <t>23,3; 28,37</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,41; 26,58</t>
+          <t>23,99; 28,27</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>10,91%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>15,65; 21,88</t>
+          <t>15,65; 21,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>26,54; 33,52</t>
+          <t>26,44; 33,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32,58; 39,47</t>
+          <t>32,86; 39,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,49; 17,87</t>
+          <t>14,39; 19,67</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,64; 11,93</t>
+          <t>7,69; 11,84</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,63; 20,16</t>
+          <t>14,6; 19,83</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,08; 24,71</t>
+          <t>19,14; 24,9</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,85; 6,51</t>
+          <t>3,77; 6,4</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11,98; 15,74</t>
+          <t>12,19; 15,73</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21,42; 25,97</t>
+          <t>21,06; 25,34</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26,52; 30,89</t>
+          <t>26,48; 31,06</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,9; 11,61</t>
+          <t>9,27; 12,36</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>25,07%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>19,56; 22,49</t>
+          <t>19,52; 22,43</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>25,84; 29,09</t>
+          <t>25,79; 29,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30,71; 34,14</t>
+          <t>30,9; 34,2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21,24; 29,71</t>
+          <t>27,31; 30,75</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11,0; 13,21</t>
+          <t>10,89; 13,16</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,71; 16,05</t>
+          <t>13,77; 16,28</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,24; 19,87</t>
+          <t>17,19; 19,88</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15,97; 21,81</t>
+          <t>20,1; 22,41</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>15,48; 17,36</t>
+          <t>15,46; 17,27</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>20,05; 22,17</t>
+          <t>20,1; 22,11</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>24,2; 26,41</t>
+          <t>24,29; 26,38</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>20,28; 25,16</t>
+          <t>24,01; 26,1</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77469</t>
+          <t>78763</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>77364</t>
+          <t>77424</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>154833</t>
+          <t>156187</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>41940; 69426</t>
+          <t>41187; 68649</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>68895; 102970</t>
+          <t>69689; 103300</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>75255; 109637</t>
+          <t>74388; 108399</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>62694; 94244</t>
+          <t>63512; 94837</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>29334; 52839</t>
+          <t>28276; 51535</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16806; 36732</t>
+          <t>16952; 38014</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28888; 52408</t>
+          <t>27712; 53326</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>64989; 90416</t>
+          <t>65978; 89932</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>76402; 111791</t>
+          <t>76137; 111666</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>93967; 133437</t>
+          <t>93238; 134140</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>109042; 150883</t>
+          <t>109858; 152071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>135184; 175178</t>
+          <t>137902; 177455</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>208941</t>
+          <t>221507</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>157180</t>
+          <t>170208</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>366121</t>
+          <t>391715</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>104999; 144529</t>
+          <t>106596; 147918</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>103762; 143181</t>
+          <t>103430; 141377</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>124199; 168103</t>
+          <t>127608; 166762</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>180391; 237390</t>
+          <t>193835; 248336</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>56593; 87616</t>
+          <t>55988; 87253</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>50814; 86872</t>
+          <t>52455; 85477</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>66147; 98814</t>
+          <t>65193; 99185</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>140027; 177113</t>
+          <t>149806; 191211</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>169398; 220959</t>
+          <t>172435; 220435</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>164720; 217491</t>
+          <t>167704; 218428</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>201964; 254614</t>
+          <t>204435; 255240</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>333121; 399678</t>
+          <t>356307; 427538</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>104026</t>
+          <t>102049</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>98969</t>
+          <t>103749</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>202995</t>
+          <t>205798</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>47375; 75477</t>
+          <t>45439; 75887</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>67165; 98040</t>
+          <t>68459; 98674</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>111742; 146178</t>
+          <t>111398; 144735</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>88559; 120478</t>
+          <t>86074; 118741</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18087; 37788</t>
+          <t>16644; 36126</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24189; 49818</t>
+          <t>24698; 49398</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>60725; 91434</t>
+          <t>59884; 90658</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>84964; 113820</t>
+          <t>88598; 116891</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>68946; 106019</t>
+          <t>69417; 105737</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>99994; 139324</t>
+          <t>99851; 140053</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181023; 228990</t>
+          <t>178595; 225962</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>183896; 224717</t>
+          <t>185286; 227315</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>101257</t>
+          <t>118111</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>69194</t>
+          <t>77723</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>170451</t>
+          <t>195834</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>59011; 91202</t>
+          <t>59579; 89935</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>93403; 130589</t>
+          <t>91976; 130132</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>99270; 136456</t>
+          <t>98760; 137888</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>81245; 121159</t>
+          <t>94602; 143306</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>55734; 84101</t>
+          <t>55574; 84251</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36533; 63359</t>
+          <t>36715; 64001</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38400; 66325</t>
+          <t>38638; 66689</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>43141; 90449</t>
+          <t>63153; 91386</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>122086; 164157</t>
+          <t>120854; 163986</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>137609; 183836</t>
+          <t>138032; 184873</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>146457; 193190</t>
+          <t>145379; 191763</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>121410; 203012</t>
+          <t>168258; 226159</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41625</t>
+          <t>48120</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>47515</t>
+          <t>51282</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>89140</t>
+          <t>99403</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>31753; 55612</t>
+          <t>29798; 53609</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>29623; 52754</t>
+          <t>30232; 52337</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>63065; 90728</t>
+          <t>62218; 90252</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33277; 51357</t>
+          <t>38053; 58910</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>14250; 32905</t>
+          <t>14249; 32020</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23915; 44286</t>
+          <t>23333; 44721</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29658; 52438</t>
+          <t>30420; 52884</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>25661; 62827</t>
+          <t>43053; 59879</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>51105; 81412</t>
+          <t>51407; 79479</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>58473; 89687</t>
+          <t>59197; 90270</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>99627; 135657</t>
+          <t>99659; 135875</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>59748; 106948</t>
+          <t>86164; 112968</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>108544</t>
+          <t>110107</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>95534</t>
+          <t>96874</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>204078</t>
+          <t>206981</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>36349; 61183</t>
+          <t>35475; 61289</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>65543; 99318</t>
+          <t>69283; 99893</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>52581; 81784</t>
+          <t>53035; 81321</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>92266; 122737</t>
+          <t>95087; 124023</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>25747; 48892</t>
+          <t>26032; 47556</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>39431; 67552</t>
+          <t>39410; 65424</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22048; 43582</t>
+          <t>22495; 43648</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>84746; 109064</t>
+          <t>84638; 109500</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>67263; 102249</t>
+          <t>68411; 100270</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>112501; 155293</t>
+          <t>114064; 157664</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>79895; 117065</t>
+          <t>81005; 116590</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>186214; 222961</t>
+          <t>189340; 225895</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>174609</t>
+          <t>210694</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>153210</t>
+          <t>177953</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>327819</t>
+          <t>388647</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>122988; 166645</t>
+          <t>123715; 165328</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>158231; 208246</t>
+          <t>159304; 207366</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>161502; 212311</t>
+          <t>167616; 215108</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>149464; 197972</t>
+          <t>184519; 237832</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>53500; 85452</t>
+          <t>53532; 84427</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>102849; 145062</t>
+          <t>101660; 147076</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>138010; 180688</t>
+          <t>136563; 179750</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>78233; 210099</t>
+          <t>159425; 200730</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>185182; 238563</t>
+          <t>186615; 238845</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>274663; 335323</t>
+          <t>273514; 335473</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>317327; 383273</t>
+          <t>313347; 381499</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>212344; 391704</t>
+          <t>357844; 421726</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>115759</t>
+          <t>135909</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>36363</t>
+          <t>41806</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>152122</t>
+          <t>177715</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>116251; 162547</t>
+          <t>116285; 160192</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>206787; 261125</t>
+          <t>206000; 259945</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>253644; 307319</t>
+          <t>255819; 308874</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>50961; 165997</t>
+          <t>114804; 157020</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>59892; 93498</t>
+          <t>60283; 92791</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>120199; 165644</t>
+          <t>119986; 162951</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>157594; 204161</t>
+          <t>158146; 205709</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>27615; 46736</t>
+          <t>31352; 53240</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>182938; 240295</t>
+          <t>186053; 240150</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>342880; 415827</t>
+          <t>337162; 405732</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>425627; 495660</t>
+          <t>424934; 498476</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>97086; 191103</t>
+          <t>151080; 201444</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>932230</t>
+          <t>1025259</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>735328</t>
+          <t>797020</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1667558</t>
+          <t>1822280</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>640571; 736856</t>
+          <t>639436; 734655</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>885148; 996643</t>
+          <t>883601; 998295</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1039782; 1155736</t>
+          <t>1046073; 1157803</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>734467; 1027734</t>
+          <t>964591; 1085978</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>371045; 445792</t>
+          <t>367576; 444153</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>487569; 570891</t>
+          <t>489634; 579077</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>610279; 703337</t>
+          <t>608342; 703798</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>592589; 809525</t>
+          <t>750751; 837236</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1029471; 1154499</t>
+          <t>1027807; 1148678</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1400238; 1548024</t>
+          <t>1403293; 1543968</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1676119; 1828966</t>
+          <t>1681725; 1826660</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1453819; 1803776</t>
+          <t>1744970; 1897108</t>
         </is>
       </c>
     </row>
